--- a/Skipily_Business_Model2 2.xlsx
+++ b/Skipily_Business_Model2 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekkehart/Documents/01-Projekte/Programmieren/BoatCare/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0AE137-B521-0E44-AECA-D81012C74B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691581B9-D11D-9048-9883-2D403B54463C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9780" yWindow="940" windowWidth="28360" windowHeight="18720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9780" yWindow="940" windowWidth="28360" windowHeight="18720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Annahmen" sheetId="1" r:id="rId1"/>
@@ -621,27 +621,32 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -649,16 +654,19 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -728,9 +736,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -908,19 +916,19 @@
                 <c:formatCode>"€"#,##0;\("€"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>594750.13500000001</c:v>
+                  <c:v>294750.13500000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1283918.07125</c:v>
+                  <c:v>893918.07125000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2631840.8670000001</c:v>
+                  <c:v>1919840.8670000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4258232.0930000003</c:v>
+                  <c:v>3300232.0930000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5409396.4780000001</c:v>
+                  <c:v>4355396.4780000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -984,19 +992,19 @@
                 <c:formatCode>"€"#,##0;\("€"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-741398.4542588474</c:v>
+                  <c:v>-235899.50817326963</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12813212.13124685</c:v>
+                  <c:v>-5872722.2268214729</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5564738.7851692578</c:v>
+                  <c:v>2178333.6441089916</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3769932.030225195</c:v>
+                  <c:v>1381311.0745666388</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2935053.5681276959</c:v>
+                  <c:v>1082630.5377045872</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1190,19 +1198,19 @@
                 <c:formatCode>"€"#,##0;\("€"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-497635.13500000001</c:v>
+                  <c:v>-197635.13500000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-750001.82125000004</c:v>
+                  <c:v>-360001.82125000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-780817.86700000009</c:v>
+                  <c:v>-68817.867000000086</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>326984.90699999966</c:v>
+                  <c:v>1284984.9069999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3266385.5219999999</c:v>
+                  <c:v>4320385.5219999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1266,19 +1274,19 @@
                 <c:formatCode>"€"#,##0;\("€"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-497635.13500000001</c:v>
+                  <c:v>-197635.13500000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-1247636.95625</c:v>
+                  <c:v>-557636.95625000005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2028454.8232500001</c:v>
+                  <c:v>-626454.82325000013</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1701469.9162500005</c:v>
+                  <c:v>658530.08374999953</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1564915.6057499994</c:v>
+                  <c:v>4978915.6057499992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1472,19 +1480,19 @@
                 <c:formatCode>"€"#,##0;\("€"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1252364.865</c:v>
+                  <c:v>1552364.865</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>502363.04374999995</c:v>
+                  <c:v>1192363.04375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4721545.1767499996</c:v>
+                  <c:v>6123545.1767499996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5048530.0837499993</c:v>
+                  <c:v>7408530.0837499993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8314915.6057499992</c:v>
+                  <c:v>11728915.605749998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1677,19 +1685,19 @@
                 <c:formatCode>"€"#,##0;\("€"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>440000</c:v>
+                  <c:v>140000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>720000</c:v>
+                  <c:v>330000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1170000</c:v>
+                  <c:v>458000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1512000</c:v>
+                  <c:v>554000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1670000</c:v>
+                  <c:v>616000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2296,14 +2304,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="24"/>
@@ -2365,7 +2373,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="24"/>
@@ -2416,7 +2424,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="25" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="24"/>
@@ -2456,7 +2464,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="24"/>
@@ -2573,7 +2581,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="24"/>
@@ -2582,7 +2590,7 @@
       <c r="E1" s="24"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="25" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="24"/>
@@ -2662,7 +2670,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="25" t="s">
         <v>57</v>
       </c>
       <c r="B9" s="24"/>
@@ -2760,7 +2768,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="25" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="24"/>
@@ -2847,7 +2855,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="24"/>
@@ -3123,7 +3131,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="23" t="s">
         <v>99</v>
       </c>
       <c r="B17" s="24"/>
@@ -3202,7 +3210,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>110</v>
       </c>
       <c r="B1" s="24"/>
@@ -3232,7 +3240,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="25" t="s">
         <v>112</v>
       </c>
       <c r="B4" s="24"/>
@@ -3245,20 +3253,18 @@
       <c r="A5" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="7">
-        <v>220000</v>
-      </c>
+      <c r="B5" s="7"/>
       <c r="C5" s="7">
-        <v>320000</v>
+        <v>100000</v>
       </c>
       <c r="D5" s="7">
-        <v>480000</v>
+        <v>100000</v>
       </c>
       <c r="E5" s="7">
-        <v>600000</v>
+        <v>100000</v>
       </c>
       <c r="F5" s="7">
-        <v>660000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -3269,16 +3275,16 @@
         <v>60000</v>
       </c>
       <c r="C6" s="7">
-        <v>140000</v>
+        <v>60000</v>
       </c>
       <c r="D6" s="7">
-        <v>260000</v>
+        <v>60000</v>
       </c>
       <c r="E6" s="7">
-        <v>360000</v>
+        <v>60000</v>
       </c>
       <c r="F6" s="7">
-        <v>380000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -3305,21 +3311,11 @@
       <c r="A8" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="7">
-        <v>80000</v>
-      </c>
-      <c r="C8" s="7">
-        <v>90000</v>
-      </c>
-      <c r="D8" s="7">
-        <v>120000</v>
-      </c>
-      <c r="E8" s="7">
-        <v>140000</v>
-      </c>
-      <c r="F8" s="7">
-        <v>150000</v>
-      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -3332,13 +3328,13 @@
         <v>18000</v>
       </c>
       <c r="D9" s="7">
-        <v>30000</v>
+        <v>18000</v>
       </c>
       <c r="E9" s="7">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="F9" s="7">
-        <v>42000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -3427,27 +3423,27 @@
       </c>
       <c r="B14" s="14">
         <f>SUM(B5:B13)</f>
-        <v>440000</v>
+        <v>140000</v>
       </c>
       <c r="C14" s="14">
         <f>SUM(C5:C13)</f>
-        <v>720000</v>
+        <v>330000</v>
       </c>
       <c r="D14" s="14">
         <f>SUM(D5:D13)</f>
-        <v>1170000</v>
+        <v>458000</v>
       </c>
       <c r="E14" s="14">
         <f>SUM(E5:E13)</f>
-        <v>1512000</v>
+        <v>554000</v>
       </c>
       <c r="F14" s="14">
         <f>SUM(F5:F13)</f>
-        <v>1670000</v>
+        <v>616000</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="25" t="s">
         <v>123</v>
       </c>
       <c r="B16" s="24"/>
@@ -3662,23 +3658,23 @@
       </c>
       <c r="B26" s="17">
         <f>B14+B24</f>
-        <v>594750.13500000001</v>
+        <v>294750.13500000001</v>
       </c>
       <c r="C26" s="17">
         <f>C14+C24</f>
-        <v>1283918.07125</v>
+        <v>893918.07125000004</v>
       </c>
       <c r="D26" s="17">
         <f>D14+D24</f>
-        <v>2631840.8670000001</v>
+        <v>1919840.8670000001</v>
       </c>
       <c r="E26" s="17">
         <f>E14+E24</f>
-        <v>4258232.0930000003</v>
+        <v>3300232.0930000003</v>
       </c>
       <c r="F26" s="17">
         <f>F14+F24</f>
-        <v>5409396.4780000001</v>
+        <v>4355396.4780000001</v>
       </c>
     </row>
   </sheetData>
@@ -3701,7 +3697,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>133</v>
       </c>
       <c r="B1" s="24"/>
@@ -3731,7 +3727,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="25" t="s">
         <v>135</v>
       </c>
       <c r="B4" s="24"/>
@@ -3886,7 +3882,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="25" t="s">
         <v>142</v>
       </c>
       <c r="B12" s="24"/>
@@ -3961,7 +3957,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="25" t="s">
         <v>146</v>
       </c>
       <c r="B17" s="24"/>
@@ -4116,7 +4112,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="25" t="s">
         <v>153</v>
       </c>
       <c r="B25" s="24"/>
@@ -4347,7 +4343,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>161</v>
       </c>
       <c r="B1" s="24"/>
@@ -4482,23 +4478,23 @@
       </c>
       <c r="B8" s="16">
         <f>-'4_Kosten'!B14</f>
-        <v>-440000</v>
+        <v>-140000</v>
       </c>
       <c r="C8" s="16">
         <f>-'4_Kosten'!C14</f>
-        <v>-720000</v>
+        <v>-330000</v>
       </c>
       <c r="D8" s="16">
         <f>-'4_Kosten'!D14</f>
-        <v>-1170000</v>
+        <v>-458000</v>
       </c>
       <c r="E8" s="16">
         <f>-'4_Kosten'!E14</f>
-        <v>-1512000</v>
+        <v>-554000</v>
       </c>
       <c r="F8" s="16">
         <f>-'4_Kosten'!F14</f>
-        <v>-1670000</v>
+        <v>-616000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -4507,23 +4503,23 @@
       </c>
       <c r="B9" s="14">
         <f>B6+B8</f>
-        <v>-497635.13500000001</v>
+        <v>-197635.13500000001</v>
       </c>
       <c r="C9" s="14">
         <f>C6+C8</f>
-        <v>-750001.82125000004</v>
+        <v>-360001.82125000004</v>
       </c>
       <c r="D9" s="14">
         <f>D6+D8</f>
-        <v>-780817.86700000009</v>
+        <v>-68817.867000000086</v>
       </c>
       <c r="E9" s="14">
         <f>E6+E8</f>
-        <v>326984.90699999966</v>
+        <v>1284984.9069999997</v>
       </c>
       <c r="F9" s="14">
         <f>F6+F8</f>
-        <v>3266385.5219999999</v>
+        <v>4320385.5219999999</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -4532,27 +4528,27 @@
       </c>
       <c r="B10" s="21">
         <f>IFERROR(B9/B4,0)</f>
-        <v>-5.1241840601348914</v>
+        <v>-2.0350629151006538</v>
       </c>
       <c r="C10" s="21">
         <f>IFERROR(C9/C4,0)</f>
-        <v>-1.4047181018558623</v>
+        <v>-0.67426646267087775</v>
       </c>
       <c r="D10" s="21">
         <f>IFERROR(D9/D4,0)</f>
-        <v>-0.42183045105328248</v>
+        <v>-3.7178288438339278E-2</v>
       </c>
       <c r="E10" s="21">
         <f>IFERROR(E9/E4,0)</f>
-        <v>7.1312853241187857E-2</v>
+        <v>0.28024516767690594</v>
       </c>
       <c r="F10" s="21">
         <f>IFERROR(F9/F4,0)</f>
-        <v>0.37649465166367713</v>
+        <v>0.49798225935137602</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="25" t="s">
         <v>169</v>
       </c>
       <c r="B12" s="24"/>
@@ -4567,23 +4563,23 @@
       </c>
       <c r="B13" s="10">
         <f>B9</f>
-        <v>-497635.13500000001</v>
+        <v>-197635.13500000001</v>
       </c>
       <c r="C13" s="10">
         <f>B13+C9</f>
-        <v>-1247636.95625</v>
+        <v>-557636.95625000005</v>
       </c>
       <c r="D13" s="10">
         <f>C13+D9</f>
-        <v>-2028454.8232500001</v>
+        <v>-626454.82325000013</v>
       </c>
       <c r="E13" s="10">
         <f>D13+E9</f>
-        <v>-1701469.9162500005</v>
+        <v>658530.08374999953</v>
       </c>
       <c r="F13" s="10">
         <f>E13+F9</f>
-        <v>1564915.6057499994</v>
+        <v>4978915.6057499992</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -4637,27 +4633,27 @@
       </c>
       <c r="B16" s="10">
         <f>B15+B13</f>
-        <v>1252364.865</v>
+        <v>1552364.865</v>
       </c>
       <c r="C16" s="10">
         <f>C15+C13</f>
-        <v>502363.04374999995</v>
+        <v>1192363.04375</v>
       </c>
       <c r="D16" s="10">
         <f>D15+D13</f>
-        <v>4721545.1767499996</v>
+        <v>6123545.1767499996</v>
       </c>
       <c r="E16" s="10">
         <f>E15+E13</f>
-        <v>5048530.0837499993</v>
+        <v>7408530.0837499993</v>
       </c>
       <c r="F16" s="10">
         <f>F15+F13</f>
-        <v>8314915.6057499992</v>
+        <v>11728915.605749998</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="25" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="24"/>
@@ -4672,23 +4668,23 @@
       </c>
       <c r="B19" s="10">
         <f>IFERROR(-B8/IFERROR(B6/B4,0),0)</f>
-        <v>-741398.4542588474</v>
+        <v>-235899.50817326963</v>
       </c>
       <c r="C19" s="10">
         <f>IFERROR(-C8/IFERROR(C6/C4,0),0)</f>
-        <v>-12813212.13124685</v>
+        <v>-5872722.2268214729</v>
       </c>
       <c r="D19" s="10">
         <f>IFERROR(-D8/IFERROR(D6/D4,0),0)</f>
-        <v>5564738.7851692578</v>
+        <v>2178333.6441089916</v>
       </c>
       <c r="E19" s="10">
         <f>IFERROR(-E8/IFERROR(E6/E4,0),0)</f>
-        <v>3769932.030225195</v>
+        <v>1381311.0745666388</v>
       </c>
       <c r="F19" s="10">
         <f>IFERROR(-F8/IFERROR(F6/F4,0),0)</f>
-        <v>2935053.5681276959</v>
+        <v>1082630.5377045872</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -4722,23 +4718,23 @@
       </c>
       <c r="B21" s="10">
         <f>B4-B19</f>
-        <v>838513.4542588474</v>
+        <v>333014.50817326963</v>
       </c>
       <c r="C21" s="10">
         <f>C4-C19</f>
-        <v>13347128.38124685</v>
+        <v>6406638.4768214729</v>
       </c>
       <c r="D21" s="10">
         <f>D4-D19</f>
-        <v>-3713715.7851692578</v>
+        <v>-327310.6441089916</v>
       </c>
       <c r="E21" s="10">
         <f>E4-E19</f>
-        <v>815284.96977480501</v>
+        <v>3203905.925433361</v>
       </c>
       <c r="F21" s="10">
         <f>F4-F19</f>
-        <v>5740728.4318723045</v>
+        <v>7593151.462295413</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -4770,7 +4766,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>179</v>
       </c>
       <c r="B1" s="24"/>
@@ -4830,23 +4826,23 @@
       </c>
       <c r="B5" s="16">
         <f>'4_Kosten'!B14</f>
-        <v>440000</v>
+        <v>140000</v>
       </c>
       <c r="C5" s="16">
         <f>'4_Kosten'!C14</f>
-        <v>720000</v>
+        <v>330000</v>
       </c>
       <c r="D5" s="16">
         <f>'4_Kosten'!D14</f>
-        <v>1170000</v>
+        <v>458000</v>
       </c>
       <c r="E5" s="16">
         <f>'4_Kosten'!E14</f>
-        <v>1512000</v>
+        <v>554000</v>
       </c>
       <c r="F5" s="16">
         <f>'4_Kosten'!F14</f>
-        <v>1670000</v>
+        <v>616000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -4880,23 +4876,23 @@
       </c>
       <c r="B7" s="16">
         <f>'4_Kosten'!B26</f>
-        <v>594750.13500000001</v>
+        <v>294750.13500000001</v>
       </c>
       <c r="C7" s="16">
         <f>'4_Kosten'!C26</f>
-        <v>1283918.07125</v>
+        <v>893918.07125000004</v>
       </c>
       <c r="D7" s="16">
         <f>'4_Kosten'!D26</f>
-        <v>2631840.8670000001</v>
+        <v>1919840.8670000001</v>
       </c>
       <c r="E7" s="16">
         <f>'4_Kosten'!E26</f>
-        <v>4258232.0930000003</v>
+        <v>3300232.0930000003</v>
       </c>
       <c r="F7" s="16">
         <f>'4_Kosten'!F26</f>
-        <v>5409396.4780000001</v>
+        <v>4355396.4780000001</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -4905,23 +4901,23 @@
       </c>
       <c r="B8" s="16">
         <f>'6_GuV_Breakeven'!B9</f>
-        <v>-497635.13500000001</v>
+        <v>-197635.13500000001</v>
       </c>
       <c r="C8" s="16">
         <f>'6_GuV_Breakeven'!C9</f>
-        <v>-750001.82125000004</v>
+        <v>-360001.82125000004</v>
       </c>
       <c r="D8" s="16">
         <f>'6_GuV_Breakeven'!D9</f>
-        <v>-780817.86700000009</v>
+        <v>-68817.867000000086</v>
       </c>
       <c r="E8" s="16">
         <f>'6_GuV_Breakeven'!E9</f>
-        <v>326984.90699999966</v>
+        <v>1284984.9069999997</v>
       </c>
       <c r="F8" s="16">
         <f>'6_GuV_Breakeven'!F9</f>
-        <v>3266385.5219999999</v>
+        <v>4320385.5219999999</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -4930,23 +4926,23 @@
       </c>
       <c r="B9" s="16">
         <f>'6_GuV_Breakeven'!B13</f>
-        <v>-497635.13500000001</v>
+        <v>-197635.13500000001</v>
       </c>
       <c r="C9" s="16">
         <f>'6_GuV_Breakeven'!C13</f>
-        <v>-1247636.95625</v>
+        <v>-557636.95625000005</v>
       </c>
       <c r="D9" s="16">
         <f>'6_GuV_Breakeven'!D13</f>
-        <v>-2028454.8232500001</v>
+        <v>-626454.82325000013</v>
       </c>
       <c r="E9" s="16">
         <f>'6_GuV_Breakeven'!E13</f>
-        <v>-1701469.9162500005</v>
+        <v>658530.08374999953</v>
       </c>
       <c r="F9" s="16">
         <f>'6_GuV_Breakeven'!F13</f>
-        <v>1564915.6057499994</v>
+        <v>4978915.6057499992</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -4955,23 +4951,23 @@
       </c>
       <c r="B10" s="16">
         <f>'6_GuV_Breakeven'!B16</f>
-        <v>1252364.865</v>
+        <v>1552364.865</v>
       </c>
       <c r="C10" s="16">
         <f>'6_GuV_Breakeven'!C16</f>
-        <v>502363.04374999995</v>
+        <v>1192363.04375</v>
       </c>
       <c r="D10" s="16">
         <f>'6_GuV_Breakeven'!D16</f>
-        <v>4721545.1767499996</v>
+        <v>6123545.1767499996</v>
       </c>
       <c r="E10" s="16">
         <f>'6_GuV_Breakeven'!E16</f>
-        <v>5048530.0837499993</v>
+        <v>7408530.0837499993</v>
       </c>
       <c r="F10" s="16">
         <f>'6_GuV_Breakeven'!F16</f>
-        <v>8314915.6057499992</v>
+        <v>11728915.605749998</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -4980,23 +4976,23 @@
       </c>
       <c r="B11" s="16">
         <f>'6_GuV_Breakeven'!B19</f>
-        <v>-741398.4542588474</v>
+        <v>-235899.50817326963</v>
       </c>
       <c r="C11" s="16">
         <f>'6_GuV_Breakeven'!C19</f>
-        <v>-12813212.13124685</v>
+        <v>-5872722.2268214729</v>
       </c>
       <c r="D11" s="16">
         <f>'6_GuV_Breakeven'!D19</f>
-        <v>5564738.7851692578</v>
+        <v>2178333.6441089916</v>
       </c>
       <c r="E11" s="16">
         <f>'6_GuV_Breakeven'!E19</f>
-        <v>3769932.030225195</v>
+        <v>1381311.0745666388</v>
       </c>
       <c r="F11" s="16">
         <f>'6_GuV_Breakeven'!F19</f>
-        <v>2935053.5681276959</v>
+        <v>1082630.5377045872</v>
       </c>
     </row>
   </sheetData>
